--- a/template/8.5/量化业务日报-2025-08-05.xlsx
+++ b/template/8.5/量化业务日报-2025-08-05.xlsx
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>0.99862</v>
+        <v>0.99823</v>
       </c>
       <c r="C19" s="4" t="n"/>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>-0.00023%</t>
+          <t>0.03884%</t>
         </is>
       </c>
       <c r="C21" s="4" t="n"/>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>0.99309</v>
+        <v>0.99211</v>
       </c>
       <c r="C22" s="4" t="n"/>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>-0.00038%</t>
+          <t>0.0984%</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.99805</v>
       </c>
       <c r="C21" s="4" t="n"/>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>0.00012%</t>
+          <t>-0.05499%</t>
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>0.99309</v>
+        <v>0.99211</v>
       </c>
       <c r="C24" s="4" t="n"/>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>-0.11281%</t>
+          <t>-0.01415%</t>
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>0.98632</v>
+        <v>0.98612</v>
       </c>
     </row>
     <row r="19">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>-0.00035%</t>
+          <t>0.01994%</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>0.98561</v>
+        <v>0.9825</v>
       </c>
     </row>
     <row r="22">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>-0.00045%</t>
+          <t>0.31609%</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>1.00315</v>
+        <v>0.98622</v>
       </c>
     </row>
     <row r="19" ht="27" customHeight="1">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>0.00021%</t>
+          <t>1.71687%</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1.00244</v>
+        <v>0.9826</v>
       </c>
     </row>
     <row r="22" ht="27" customHeight="1">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>0.00011%</t>
+          <t>2.01924%</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>0.98965</v>
+        <v>0.9895699999999999</v>
       </c>
       <c r="C19" s="4" t="n"/>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>0.00021%</t>
+          <t>0.0083%</t>
         </is>
       </c>
       <c r="C21" s="4" t="n"/>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>0.98759</v>
+        <v>0.9882300000000001</v>
       </c>
       <c r="C22" s="4" t="n"/>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>-0.00043%</t>
+          <t>-0.0652%</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
@@ -3076,7 +3076,7 @@
   <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>0.98965</v>
+        <v>0.9895699999999999</v>
       </c>
       <c r="C19" s="4" t="n"/>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>0.00021%</t>
+          <t>0.0083%</t>
         </is>
       </c>
       <c r="C21" s="4" t="n"/>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>0.98759</v>
+        <v>0.9882300000000001</v>
       </c>
       <c r="C22" s="4" t="n"/>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>-0.00043%</t>
+          <t>-0.0652%</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>

--- a/template/8.5/量化业务日报-2025-08-05.xlsx
+++ b/template/8.5/量化业务日报-2025-08-05.xlsx
@@ -203,10 +203,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -569,61 +569,6 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9525000" cy="5715000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9525000" cy="5715000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1150,7 +1095,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>0.99823</v>
+        <v>0.99862</v>
       </c>
       <c r="C19" s="4" t="n"/>
     </row>
@@ -1173,7 +1118,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>0.03884%</t>
+          <t>-0.00023%</t>
         </is>
       </c>
       <c r="C21" s="4" t="n"/>
@@ -1185,7 +1130,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>0.99211</v>
+        <v>0.99309</v>
       </c>
       <c r="C22" s="4" t="n"/>
     </row>
@@ -1208,7 +1153,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>0.0984%</t>
+          <t>-0.00038%</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
@@ -1548,7 +1493,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>-123168.0599999996</v>
+        <v>-123723.0599999996</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>-117187.35</v>
@@ -1638,7 +1583,7 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>0.99805</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="C21" s="4" t="n"/>
     </row>
@@ -1661,7 +1606,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>-0.05499%</t>
+          <t>0.00012%</t>
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
@@ -1673,7 +1618,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>0.99211</v>
+        <v>0.99309</v>
       </c>
       <c r="C24" s="4" t="n"/>
     </row>
@@ -1696,7 +1641,7 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>-0.01415%</t>
+          <t>-0.11281%</t>
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
@@ -2051,7 +1996,7 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>0.98612</v>
+        <v>0.98632</v>
       </c>
     </row>
     <row r="19">
@@ -2072,7 +2017,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>0.01994%</t>
+          <t>-0.00035%</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2028,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>0.9825</v>
+        <v>0.98561</v>
       </c>
     </row>
     <row r="22">
@@ -2104,7 +2049,7 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>0.31609%</t>
+          <t>-0.00045%</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2375,7 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>0.98622</v>
+        <v>1.00315</v>
       </c>
     </row>
     <row r="19" ht="27" customHeight="1">
@@ -2451,7 +2396,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>1.71687%</t>
+          <t>0.00021%</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2407,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>0.9826</v>
+        <v>1.00244</v>
       </c>
     </row>
     <row r="22" ht="27" customHeight="1">
@@ -2483,7 +2428,7 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>2.01924%</t>
+          <t>0.00011%</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2801,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>0.9895699999999999</v>
+        <v>0.98965</v>
       </c>
       <c r="C19" s="4" t="n"/>
     </row>
@@ -2879,7 +2824,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>0.0083%</t>
+          <t>0.00021%</t>
         </is>
       </c>
       <c r="C21" s="4" t="n"/>
@@ -2891,7 +2836,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>0.9882300000000001</v>
+        <v>0.98759</v>
       </c>
       <c r="C22" s="4" t="n"/>
     </row>
@@ -2914,7 +2859,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>-0.0652%</t>
+          <t>-0.00043%</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
@@ -3073,7 +3018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3104,8 +3049,16 @@
           <t>一、账户资产及收益情况</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="4" t="n"/>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>一、账户资产及收益情况</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>一、账户资产及收益情况</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="27" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -3118,7 +3071,11 @@
           <t>量化三</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>账户名称</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="27" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -3129,7 +3086,11 @@
       <c r="B4" s="6" t="n">
         <v>85016</v>
       </c>
-      <c r="C4" s="4" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>账户编号</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="27" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -3144,7 +3105,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>量化三股票单元</t>
+          <t>资产单元名称</t>
         </is>
       </c>
     </row>
@@ -3155,10 +3116,12 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>4098260.56</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>850000</v>
+        <v>5000333</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>单元资产净值</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="27" customHeight="1">
@@ -3172,7 +3135,11 @@
           <t>账户资产净值</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>账户资产净值</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="27" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -3180,11 +3147,15 @@
           <t>返息</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>9999</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>156502.08</v>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>返息</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>返息</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
@@ -3193,203 +3164,271 @@
           <t>手续费</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
-        <v>333</v>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>手续费</t>
+        </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+          <t>手续费</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="n"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="n"/>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>总盈利/亏损(含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
-        <v>-51739.43999999948</v>
-      </c>
-      <c r="C10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>收益率(含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>-1.0348%</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>总盈利/亏损(不含返息、逆回购、手续费)</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>-62071.43999999948</v>
-      </c>
-      <c r="C12" s="4" t="n"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>收益率(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>收益率(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="27" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>收益率(不含返息、逆回购、手续费)</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>-1.2414%</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n"/>
+          <t>盈利/亏损(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>840001</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>盈利/亏损(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>二、净值列示</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="4" t="n"/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="27" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>实收资本</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="C15" s="4" t="n"/>
+          <t>收益率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>收益率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>收益率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>资产净值</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>4948260.560000001</v>
-      </c>
-      <c r="C16" s="4" t="n"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>二、净值列示</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>二、净值列示</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>二、净值列示</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="27" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>总份额</t>
+          <t>实收资本</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
         <v>5000000</v>
       </c>
-      <c r="C17" s="4" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>实收资本</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="27" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>资产净值</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>5000333</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>资产净值</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>总份额</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>总份额</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
           <t>期初单位净值</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="4" t="n"/>
-    </row>
-    <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>昨日单位净值(含返息、逆回购、手续费)</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>0.9895699999999999</v>
-      </c>
-      <c r="C19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>单位净值(含返息、逆回购、手续费)</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n">
-        <v>0.98965</v>
-      </c>
-      <c r="C20" s="4" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>期初单位净值</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="27" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>昨日单位净值(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>昨日单位净值(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="27" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>单位净值(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>单位净值(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>日净值增长率(含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>0.0083%</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="27" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>昨日单位净值(不含返息、逆回购、手续费)</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="n">
-        <v>0.9882300000000001</v>
-      </c>
-      <c r="C22" s="4" t="n"/>
-    </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>单位净值(不含返息、逆回购、手续费)</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="n">
-        <v>0.98759</v>
-      </c>
-      <c r="C23" s="4" t="n"/>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>-200.00666%</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>日净值增长率(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="27" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>日净值增长率(不含返息、逆回购、手续费)</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>-0.0652%</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n"/>
+          <t>昨日单位净值(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>昨日单位净值(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="27" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>三、保证金使用情况</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="4" t="n"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>单位净值(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>单位净值(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>单位净值(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="27" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>占用</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n">
-        <v>0</v>
+          <t>日净值增长率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含返息、逆回购、手续费)</t>
+        </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -3398,13 +3437,15 @@
       </c>
     </row>
     <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>账户权益</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n">
-        <v>5000333</v>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>三、保证金使用情况</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>三、保证金使用情况</t>
+        </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -3415,36 +3456,78 @@
     <row r="28" ht="27" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
+          <t>占用</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>占用</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="27" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>账户权益</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>账户权益</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>账户权益</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="27" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t>风险度</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="27" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>风险度</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>风险度</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="27" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="175" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>四、交易情况</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>四、交易情况</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="175" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>今日交易 1 只期货, 成交合约价值 3137.6 万元,其中
 1.国债期货:无
@@ -3455,28 +3538,36 @@
 4.其他品种:无</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>买入股票: 0 只, 卖出股票: 0 只, 股票合计成交金额: 0 万元</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="27" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33" ht="27" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="4" t="n"/>
-    </row>
-    <row r="32" ht="125" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>五、持仓情况</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>五、持仓情况</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="125" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">共持仓: 0 只期货, 持仓合约价值 0.0 万元, 其中: 
 国债期货 0只 
@@ -3485,39 +3576,17 @@
 其他品种 0只 </t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>股票: 0 只</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B4:C4"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3537,28 +3606,28 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>量化二持仓信息</t>
         </is>
       </c>
-      <c r="B1" s="19" t="n"/>
-      <c r="C1" s="19" t="n"/>
-      <c r="D1" s="19" t="n"/>
+      <c r="B1" s="18" t="n"/>
+      <c r="C1" s="18" t="n"/>
+      <c r="D1" s="18" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>统计日期</t>
         </is>
       </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="C2" s="19" t="n"/>
-      <c r="D2" s="19" t="inlineStr">
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="inlineStr">
         <is>
           <t>单位：万元</t>
         </is>
@@ -3715,88 +3784,88 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>汇总</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>风险度：</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>4.8957%</t>
         </is>
       </c>
-      <c r="C13" s="19" t="n"/>
-      <c r="D13" s="19" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>权益：</t>
         </is>
       </c>
-      <c r="B14" s="19" t="n">
+      <c r="B14" s="18" t="n">
         <v>986.3200000000001</v>
       </c>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>当日盈亏：</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n">
+      <c r="B15" s="18" t="n">
         <v>0.89</v>
       </c>
-      <c r="C15" s="19" t="n"/>
-      <c r="D15" s="19" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>总市值：</t>
         </is>
       </c>
-      <c r="B16" s="19" t="n">
+      <c r="B16" s="18" t="n">
         <v>580.76</v>
       </c>
-      <c r="C16" s="19" t="n"/>
-      <c r="D16" s="19" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>去锁市值：</t>
         </is>
       </c>
-      <c r="B17" s="19" t="n">
+      <c r="B17" s="18" t="n">
         <v>580.76</v>
       </c>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="19" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>平仓盈亏：</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n">
+      <c r="B18" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3823,25 +3892,25 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>量化二持仓信息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>统计日期</t>
         </is>
       </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="C2" s="19" t="n"/>
-      <c r="D2" s="19" t="inlineStr">
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="inlineStr">
         <is>
           <t>单位：万元</t>
         </is>
@@ -4029,89 +4098,89 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>汇总</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>风险度：</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>4.8957%</t>
         </is>
       </c>
-      <c r="C13" s="19" t="n"/>
-      <c r="D13" s="19" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>权益：</t>
         </is>
       </c>
-      <c r="B14" s="19" t="n">
+      <c r="B14" s="18" t="n">
         <v>986.3200000000001</v>
       </c>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>当日盈亏：</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n">
+      <c r="B15" s="18" t="n">
         <v>0.89</v>
       </c>
-      <c r="C15" s="19" t="n"/>
-      <c r="D15" s="19" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>总市值：</t>
         </is>
       </c>
-      <c r="B16" s="19" t="n">
+      <c r="B16" s="18" t="n">
         <v>580.76</v>
       </c>
-      <c r="C16" s="19" t="n"/>
-      <c r="D16" s="19" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>去锁市值：</t>
         </is>
       </c>
-      <c r="B17" s="19" t="n">
+      <c r="B17" s="18" t="n">
         <v>580.76</v>
       </c>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="19" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>平仓盈亏：</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n">
+      <c r="B18" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/template/8.5/量化业务日报-2025-08-05.xlsx
+++ b/template/8.5/量化业务日报-2025-08-05.xlsx
@@ -203,10 +203,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -569,6 +569,61 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3049,16 +3104,8 @@
           <t>一、账户资产及收益情况</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>一、账户资产及收益情况</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>一、账户资产及收益情况</t>
-        </is>
-      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="4" t="n"/>
     </row>
     <row r="3" ht="27" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -3071,11 +3118,7 @@
           <t>量化三</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>账户名称</t>
-        </is>
-      </c>
+      <c r="C3" s="4" t="n"/>
     </row>
     <row r="4" ht="27" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -3086,11 +3129,7 @@
       <c r="B4" s="6" t="n">
         <v>85016</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>账户编号</t>
-        </is>
-      </c>
+      <c r="C4" s="4" t="n"/>
     </row>
     <row r="5" ht="27" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -3105,7 +3144,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>资产单元名称</t>
+          <t>量化三股票单元</t>
         </is>
       </c>
     </row>
@@ -3118,10 +3157,8 @@
       <c r="B6" s="7" t="n">
         <v>5000333</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>单元资产净值</t>
-        </is>
+      <c r="C6" s="7" t="n">
+        <v>850000</v>
       </c>
     </row>
     <row r="7" ht="27" customHeight="1">
@@ -3135,11 +3172,7 @@
           <t>账户资产净值</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>账户资产净值</t>
-        </is>
-      </c>
+      <c r="C7" s="4" t="n"/>
     </row>
     <row r="8" ht="27" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -3147,15 +3180,11 @@
           <t>返息</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>返息</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>返息</t>
-        </is>
+      <c r="B8" s="7" t="n">
+        <v>9999</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>156502.08</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
@@ -3164,55 +3193,51 @@
           <t>手续费</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>手续费</t>
-        </is>
+      <c r="B9" s="7" t="n">
+        <v>333</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>手续费</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="n"/>
-      <c r="B10" s="18" t="n"/>
-      <c r="C10" s="18" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>盈利/亏损(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>850333</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>总盈利/亏损(含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>总盈利/亏损(含返息、逆回购、手续费)</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>总盈利/亏损(含返息、逆回购、手续费)</t>
-        </is>
-      </c>
+      <c r="B11" s="9" t="n">
+        <v>850333</v>
+      </c>
+      <c r="C11" s="4" t="n"/>
     </row>
     <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>收益率(含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>收益率(含返息、逆回购、手续费)</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>收益率(含返息、逆回购、手续费)</t>
-        </is>
-      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>17.0067%</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n"/>
     </row>
     <row r="13" ht="27" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
@@ -3223,45 +3248,33 @@
       <c r="B13" s="12" t="n">
         <v>840001</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>盈利/亏损(不含返息、逆回购、手续费)</t>
-        </is>
+      <c r="C13" s="12" t="n">
+        <v>-8888885</v>
       </c>
     </row>
     <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>总盈利/亏损(不含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>总盈利/亏损(不含返息、逆回购、手续费)</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>总盈利/亏损(不含返息、逆回购、手续费)</t>
-        </is>
-      </c>
+      <c r="B14" s="12" t="n">
+        <v>840001</v>
+      </c>
+      <c r="C14" s="4" t="n"/>
     </row>
     <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>收益率(不含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>收益率(不含返息、逆回购、手续费)</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>收益率(不含返息、逆回购、手续费)</t>
-        </is>
-      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>16.8%</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n"/>
     </row>
     <row r="16" ht="27" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -3269,16 +3282,8 @@
           <t>二、净值列示</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>二、净值列示</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>二、净值列示</t>
-        </is>
-      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="4" t="n"/>
     </row>
     <row r="17" ht="27" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -3289,11 +3294,7 @@
       <c r="B17" s="7" t="n">
         <v>5000000</v>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>实收资本</t>
-        </is>
-      </c>
+      <c r="C17" s="4" t="n"/>
     </row>
     <row r="18" ht="27" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -3302,13 +3303,9 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>5000333</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>资产净值</t>
-        </is>
-      </c>
+        <v>5850333</v>
+      </c>
+      <c r="C18" s="4" t="n"/>
     </row>
     <row r="19" ht="27" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -3319,11 +3316,7 @@
       <c r="B19" s="7" t="n">
         <v>5000000</v>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>总份额</t>
-        </is>
-      </c>
+      <c r="C19" s="4" t="n"/>
     </row>
     <row r="20" ht="27" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -3334,11 +3327,7 @@
       <c r="B20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>期初单位净值</t>
-        </is>
-      </c>
+      <c r="C20" s="4" t="n"/>
     </row>
     <row r="21" ht="27" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
@@ -3347,13 +3336,9 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>昨日单位净值(含返息、逆回购、手续费)</t>
-        </is>
-      </c>
+        <v>1.17007</v>
+      </c>
+      <c r="C21" s="4" t="n"/>
     </row>
     <row r="22" ht="27" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -3362,13 +3347,9 @@
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>1.00007</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>单位净值(含返息、逆回购、手续费)</t>
-        </is>
-      </c>
+        <v>1.17007</v>
+      </c>
+      <c r="C22" s="4" t="n"/>
     </row>
     <row r="23" ht="27" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
@@ -3378,14 +3359,10 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>-200.00666%</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>日净值增长率(含返息、逆回购、手续费)</t>
-        </is>
-      </c>
+          <t>-0.00029%</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n"/>
     </row>
     <row r="24" ht="27" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
@@ -3394,47 +3371,33 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>昨日单位净值(不含返息、逆回购、手续费)</t>
-        </is>
-      </c>
+        <v>1.168</v>
+      </c>
+      <c r="C24" s="4" t="n"/>
     </row>
     <row r="25" ht="27" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>单位净值(不含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>单位净值(不含返息、逆回购、手续费)</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>单位净值(不含返息、逆回购、手续费)</t>
-        </is>
-      </c>
+      <c r="B25" s="13" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="C25" s="4" t="n"/>
     </row>
     <row r="26" ht="27" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>日净值增长率(不含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>日净值增长率(不含返息、逆回购、手续费)</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>2e-05%</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n"/>
     </row>
     <row r="27" ht="27" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -3442,16 +3405,8 @@
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>三、保证金使用情况</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="4" t="n"/>
     </row>
     <row r="28" ht="27" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -3459,10 +3414,8 @@
           <t>占用</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>占用</t>
-        </is>
+      <c r="B28" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -3476,14 +3429,12 @@
           <t>账户权益</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>账户权益</t>
-        </is>
+      <c r="B29" s="7" t="n">
+        <v>5000333</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>账户权益</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3493,14 +3444,14 @@
           <t>风险度</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>风险度</t>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>风险度</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3510,16 +3461,8 @@
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>四、交易情况</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>四、交易情况</t>
-        </is>
-      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="4" t="n"/>
     </row>
     <row r="32" ht="175" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -3550,16 +3493,8 @@
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>五、持仓情况</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>五、持仓情况</t>
-        </is>
-      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="4" t="n"/>
     </row>
     <row r="34" ht="125" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -3583,10 +3518,32 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2"/>
+  <mergeCells count="22">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3606,28 +3563,28 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>量化二持仓信息</t>
         </is>
       </c>
-      <c r="B1" s="18" t="n"/>
-      <c r="C1" s="18" t="n"/>
-      <c r="D1" s="18" t="n"/>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>统计日期</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="C2" s="18" t="n"/>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>单位：万元</t>
         </is>
@@ -3784,88 +3741,88 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>汇总</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n"/>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>风险度：</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>4.8957%</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>权益：</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="19" t="n">
         <v>986.3200000000001</v>
       </c>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>当日盈亏：</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="19" t="n">
         <v>0.89</v>
       </c>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>总市值：</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="19" t="n">
         <v>580.76</v>
       </c>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>去锁市值：</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="19" t="n">
         <v>580.76</v>
       </c>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>平仓盈亏：</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3892,25 +3849,25 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>量化二持仓信息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>统计日期</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="C2" s="18" t="n"/>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>单位：万元</t>
         </is>
@@ -4098,89 +4055,89 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>汇总</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n"/>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>风险度：</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>4.8957%</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>权益：</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="19" t="n">
         <v>986.3200000000001</v>
       </c>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>当日盈亏：</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="19" t="n">
         <v>0.89</v>
       </c>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>总市值：</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="19" t="n">
         <v>580.76</v>
       </c>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>去锁市值：</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="19" t="n">
         <v>580.76</v>
       </c>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>平仓盈亏：</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/template/8.5/量化业务日报-2025-08-05.xlsx
+++ b/template/8.5/量化业务日报-2025-08-05.xlsx
@@ -2713,17 +2713,15 @@
           <t>账户资产净值</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>账户资产净值</t>
-        </is>
+      <c r="B7" s="7" t="n">
+        <v>4948260.560000001</v>
       </c>
       <c r="C7" s="4" t="n"/>
     </row>
     <row r="8" ht="27" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>返息</t>
+          <t>返息、逆回购</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
@@ -3167,17 +3165,15 @@
           <t>账户资产净值</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>账户资产净值</t>
-        </is>
+      <c r="B7" s="7" t="n">
+        <v>5850333</v>
       </c>
       <c r="C7" s="4" t="n"/>
     </row>
     <row r="8" ht="27" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>返息</t>
+          <t>返息、逆回购</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">

--- a/template/8.5/量化业务日报-2025-08-05.xlsx
+++ b/template/8.5/量化业务日报-2025-08-05.xlsx
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>333</v>
+        <v>8888888</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>-62071.44</v>
+        <v>-9107128.52</v>
       </c>
       <c r="C12" s="4" t="n"/>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>-1.2414%</t>
+          <t>-182.1426%</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>0.98759</v>
+        <v>-0.79013</v>
       </c>
       <c r="C22" s="4" t="n"/>
     </row>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>0.98759</v>
+        <v>-0.82143</v>
       </c>
       <c r="C23" s="4" t="n"/>
     </row>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>-0.00043%</t>
+          <t>3.96083%</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>333</v>
+        <v>8888888</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>840001</v>
+        <v>-8048554</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>-8888885</v>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>840001</v>
+        <v>-8205056.08</v>
       </c>
       <c r="C14" s="4" t="n"/>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>-164.1011%</t>
         </is>
       </c>
       <c r="C15" s="4" t="n"/>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1.168</v>
+        <v>-0.60971</v>
       </c>
       <c r="C24" s="4" t="n"/>
     </row>
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1.168</v>
+        <v>-0.64101</v>
       </c>
       <c r="C25" s="4" t="n"/>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>2e-05%</t>
+          <t>5.13379%</t>
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
